--- a/originales/respuestas/2025/01. Calificadas/root/Instituto Para La Economía Social.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Instituto Para La Economía Social.xlsx
@@ -433,7 +433,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t xml:space="preserve">¿Su entidad ha implementado estrategias para fomentar una cultura de innovación entre sus funcionarios y contratistas?
@@ -449,7 +449,7 @@
     <t>Instituto Distrital De Patrimonio Cultural</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -689,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -757,7 +757,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -768,6 +768,9 @@
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -5814,7 +5817,7 @@
       </c>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="28" t="s">
         <v>136</v>
       </c>
       <c r="H19" s="6"/>
@@ -8221,7 +8224,7 @@
       <c r="K2" s="19">
         <v>3.0</v>
       </c>
-      <c r="L2" s="28"/>
+      <c r="L2" s="29"/>
       <c r="M2" s="19">
         <v>5.0</v>
       </c>
@@ -8264,7 +8267,7 @@
       <c r="K3" s="20">
         <v>5.0</v>
       </c>
-      <c r="L3" s="29"/>
+      <c r="L3" s="30"/>
       <c r="M3" s="20">
         <v>5.0</v>
       </c>
@@ -8302,14 +8305,14 @@
       <c r="H4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="31" t="s">
         <v>159</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="19">
         <v>5.0</v>
       </c>
-      <c r="L4" s="28"/>
+      <c r="L4" s="29"/>
       <c r="M4" s="19">
         <v>5.0</v>
       </c>
@@ -8356,7 +8359,7 @@
       <c r="K5" s="20">
         <v>2.0</v>
       </c>
-      <c r="L5" s="29"/>
+      <c r="L5" s="30"/>
       <c r="M5" s="20">
         <v>2.0</v>
       </c>
@@ -8394,14 +8397,14 @@
       <c r="H6" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="32" t="s">
         <v>163</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="20">
         <v>2.0</v>
       </c>
-      <c r="L6" s="29"/>
+      <c r="L6" s="30"/>
       <c r="M6" s="20">
         <v>2.0</v>
       </c>
@@ -8448,7 +8451,7 @@
       <c r="K7" s="19">
         <v>1.0</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="29"/>
       <c r="M7" s="19">
         <v>1.0</v>
       </c>
@@ -8497,7 +8500,7 @@
       <c r="K8" s="19">
         <v>3.0</v>
       </c>
-      <c r="L8" s="28"/>
+      <c r="L8" s="29"/>
       <c r="M8" s="19">
         <v>3.0</v>
       </c>
